--- a/doc_extension/demo_outputs/cleaned_data.xlsx
+++ b/doc_extension/demo_outputs/cleaned_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rajesh.kumar@acme.com</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -489,12 +489,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>INV-2024-001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>priya.sharma@enterprise.org</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>INV-2024-002</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -548,124 +548,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amit Patel</t>
+          <t>Sarah Jenkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>rajesh.kumar@acme.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+91-99887-76655</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>INV-2024-003</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$520.00</t>
+          <t>$9,800.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sarah Jenkins</t>
+          <t>Suresh Reddy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sjenkins@techcorp.io</t>
+          <t>priya.sharma@enterprise.org</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>+91-91234-56780</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>INV-2024-004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>$9,800.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Suresh Reddy</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>+91-94401-23456</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>INV-2024-004</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2023-11-05</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>$750.25</t>
         </is>
@@ -682,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,7 +678,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ent_987ecb51</t>
+          <t>ent_4253f28f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -752,7 +710,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ent_d899d596</t>
+          <t>ent_f8d65d18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -784,7 +742,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ent_471662aa</t>
+          <t>ent_bc206608</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -816,7 +774,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ent_14cc41f4</t>
+          <t>ent_e8bc7f8e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -848,22 +806,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ent_39787ec8</t>
+          <t>ent_26704bde</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rajesh Kumar</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rajesh Kumar</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -873,29 +831,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ent_b8139291</t>
+          <t>ent_a789579f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -905,29 +863,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ent_26c55715</t>
+          <t>ent_20e1fab2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>$1,250.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
+          <t>$1,250.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -937,29 +895,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ent_39a3f988</t>
+          <t>ent_bbc2769f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$1,250.00</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$1,250.00</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -969,29 +927,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ent_a35b791d</t>
+          <t>ent_27339369</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1001,29 +959,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ent_80b7f6d1</t>
+          <t>ent_e6932e57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>priya.sharma@enterprise.org</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>priya.sharma@enterprise.org</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1033,29 +991,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ent_e69597a6</t>
+          <t>ent_eb44b2b1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>priya.sharma@enterprise.org</t>
+          <t>+91-91234-56780</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>priya.sharma@enterprise.org</t>
+          <t>+91-91234-56780</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1065,29 +1023,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ent_c846909e</t>
+          <t>ent_b4f7cc3b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+91-91234-56780</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+91-91234-56780</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1097,29 +1055,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ent_dfb26a04</t>
+          <t>ent_735cd2ce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>$3,400.50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>$3,400.50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1129,29 +1087,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ent_03dae1bc</t>
+          <t>ent_545a0f59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$3,400.50</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>$3,400.50</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1161,29 +1119,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ent_5c8f9f7a</t>
+          <t>ent_a46a66a7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1193,29 +1151,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ent_33d52a4e</t>
+          <t>ent_216e77aa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>+91-99887-76655</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>+91-99887-76655</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1225,29 +1183,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ent_8cb861bd</t>
+          <t>ent_c290c16b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1257,29 +1215,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ent_5ad582a3</t>
+          <t>ent_eb9ea759</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+91-99887-76655</t>
+          <t>$520.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+91-99887-76655</t>
+          <t>$520.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1289,29 +1247,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ent_5ac60bc9</t>
+          <t>ent_eb282d3e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1321,29 +1279,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ent_a60c74b5</t>
+          <t>ent_9f9decbb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$520.00</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>$520.00</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1353,29 +1311,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ent_853bf2bc</t>
+          <t>ent_a26cfa44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amit Patel</t>
+          <t>sjenkins@techcorp.io</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Amit Patel</t>
+          <t>sjenkins@techcorp.io</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1385,29 +1343,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ent_738e6070</t>
+          <t>ent_280f9025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1424,22 +1382,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ent_3858bfda</t>
+          <t>ent_5b48a6a5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1449,29 +1407,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ent_25c40232</t>
+          <t>ent_f0102749</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sjenkins@techcorp.io</t>
+          <t>$9,800.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sjenkins@techcorp.io</t>
+          <t>$9,800.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,29 +1439,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ent_5cca47b9</t>
+          <t>ent_55ce7729</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>California</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>California</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1513,29 +1471,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ent_098159d9</t>
+          <t>ent_5e53a499</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>+91-99887-76655</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>+91-99887-76655</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1545,29 +1503,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ent_8e820d20</t>
+          <t>ent_83fc9f78</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$9,800.00</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>$9,800.00</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1577,29 +1535,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ent_6b6a6d97</t>
+          <t>ent_6343f710</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sarah Jenkins</t>
+          <t>$520.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sarah Jenkins</t>
+          <t>$520.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1609,29 +1567,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ent_21c07de0</t>
+          <t>ent_3fef44d6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1641,29 +1599,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ent_8dc5bcfb</t>
+          <t>ent_c0968160</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>State</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>+91-99887-76655</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>+91-99887-76655</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1673,29 +1631,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ent_1e94a1a0</t>
+          <t>tbl_ent_3379392e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>CustomerName</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>Rajesh Kumar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>Rajesh Kumar</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1705,29 +1663,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.98</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ent_bb1a0927</t>
+          <t>tbl_ent_a59d1fd1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$520.00</t>
+          <t>+91-98765-43210</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>$520.00</t>
+          <t>+91-98765-43210</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1737,14 +1695,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ent_c6923cb8</t>
+          <t>tbl_ent_582b8539</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1754,12 +1712,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1769,29 +1727,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ent_cf12dc3d</t>
+          <t>tbl_ent_bc0afcea</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>InvoiceNo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>INV-2024-001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>INV-2024-001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1801,29 +1759,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.98</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tbl_ent_16aef1c6</t>
+          <t>tbl_ent_46204962</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>+91-98765-43210</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>+91-98765-43210</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1840,22 +1798,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tbl_ent_8446fe8a</t>
+          <t>tbl_ent_6cfeba41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>$1,250.00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>$1,250.00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1872,22 +1830,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tbl_ent_5e83a577</t>
+          <t>tbl_ent_1fe161a1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>InvoiceNo</t>
+          <t>CustomerName</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INV-2024-001</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INV-2024-001</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1904,22 +1862,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tbl_ent_b6e7d1a8</t>
+          <t>tbl_ent_8671ca0f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>+91-91234-56780</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>+91-91234-56780</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1936,22 +1894,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tbl_ent_ea3e7b40</t>
+          <t>tbl_ent_1bb47716</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>$1,250.00</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>$1,250.00</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1968,22 +1926,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tbl_ent_2f81cb67</t>
+          <t>tbl_ent_1a63cd73</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>InvoiceNo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>+91-91234-56780</t>
+          <t>INV-2024-002</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>+91-91234-56780</t>
+          <t>INV-2024-002</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2000,22 +1958,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tbl_ent_2a6afd8f</t>
+          <t>tbl_ent_dcdcb46a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2032,22 +1990,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tbl_ent_7170d138</t>
+          <t>tbl_ent_41392940</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>InvoiceNo</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INV-2024-002</t>
+          <t>$3,400.50</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INV-2024-002</t>
+          <t>$3,400.50</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2064,22 +2022,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tbl_ent_d4f79e39</t>
+          <t>tbl_ent_c67041e1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>CustomerName</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>Sarah Jenkins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>Sarah Jenkins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2096,22 +2054,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tbl_ent_f2038936</t>
+          <t>tbl_ent_62dbe8a7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$3,400.50</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>$3,400.50</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2128,22 +2086,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tbl_ent_b0d5a9a0</t>
+          <t>tbl_ent_9fe10bf6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2160,22 +2118,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tbl_ent_27d29bdb</t>
+          <t>tbl_ent_f6a81b11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>InvoiceNo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>INV-2024-003</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>INV-2024-003</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2192,22 +2150,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tbl_ent_8eadb20e</t>
+          <t>tbl_ent_7dacffca</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>InvoiceNo</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INV-2024-003</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INV-2024-003</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2224,22 +2182,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tbl_ent_d5df2474</t>
+          <t>tbl_ent_7cf9567f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>$9,800.00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>$9,800.00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2256,22 +2214,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tbl_ent_da43c6e6</t>
+          <t>tbl_ent_f76c7589</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>CustomerName</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$9,800.00</t>
+          <t>Suresh Reddy</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>$9,800.00</t>
+          <t>Suresh Reddy</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2288,22 +2246,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tbl_ent_a0bc3c6d</t>
+          <t>tbl_ent_2e48adad</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Suresh Reddy</t>
+          <t>+91-94401-23456</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Suresh Reddy</t>
+          <t>+91-94401-23456</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2320,22 +2278,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tbl_ent_51bee7cb</t>
+          <t>tbl_ent_d7c002e8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>City</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>+91-94401-23456</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>+91-94401-23456</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2352,22 +2310,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tbl_ent_d088390c</t>
+          <t>tbl_ent_6a741d07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>InvoiceNo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>INV-2024-004</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>INV-2024-004</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2384,22 +2342,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tbl_ent_94b63cb0</t>
+          <t>tbl_ent_759b85bd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>InvoiceNo</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INV-2024-004</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INV-2024-004</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2416,22 +2374,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tbl_ent_fd377346</t>
+          <t>tbl_ent_16230f15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>$750.25</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>$750.25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2440,38 +2398,6 @@
         </is>
       </c>
       <c r="F55" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>tbl_ent_949b178b</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>$750.25</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>$750.25</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
@@ -2488,7 +2414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2536,7 +2462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iss_miss_0c184f</t>
+          <t>iss_miss_5951ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2578,7 +2504,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iss_miss_1cae56</t>
+          <t>iss_miss_43c07d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2588,7 +2514,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2603,7 +2529,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Customer record 'Rajesh Kumar' is missing a contact phone number.</t>
+          <t>Customer record 'Priya Sharma' is missing an Email address.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2620,37 +2546,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>iss_miss_3abc2e</t>
+          <t>iss_dup_a25588</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9876543210']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Customer record 'Amit Patel' is missing an Email address.</t>
+          <t>Exact duplicate Phone detected: '9876543210' (Page 1 and Page 1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2662,37 +2588,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iss_miss_4c717a</t>
+          <t>iss_dup_3475c9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>+91 9123456780</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['+91 9123456780']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Customer record 'Amit Patel' is missing an Email address.</t>
+          <t>Exact duplicate Phone detected: '+91 9123456780' (Page 1 and Page 1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2704,37 +2630,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iss_miss_62314c</t>
+          <t>iss_dup_69acd7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9988776655</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9988776655']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Customer record 'Rajesh Kumar' is missing an Email address.</t>
+          <t>Exact duplicate Phone detected: '9988776655' (Page 1 and Page 1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2746,32 +2672,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iss_miss_5d2b45</t>
+          <t>iss_ndup_06e202</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>duplicate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['555-234-5678']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Customer record 'Priya Sharma' is missing an Email address.</t>
+          <t>Near-duplicate Phone (88.9% similarity): '+1-555-234-5678' vs '555-234-5678'</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2788,37 +2714,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iss_miss_d985b8</t>
+          <t>iss_fmt_98a75c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['+91-98765-43210']</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Customer record 'Sarah Jenkins' is missing an Email address.</t>
+          <t>Inconsistent phone format '9876543210'; standard E.164 is '+91-98765-43210'</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2830,37 +2756,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iss_miss_61c109</t>
+          <t>iss_fmt_a8dbb0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>+91 9123456780</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['+91-91234-56780']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Customer record 'Suresh Reddy' is missing an Email address.</t>
+          <t>Inconsistent phone format '+91 9123456780'; standard E.164 is '+91-91234-56780'</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2872,32 +2798,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iss_dup_1cfb15</t>
+          <t>iss_fmt_8fabad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rajesh Kumar</t>
+          <t>9988776655</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['Rajesh Kumar']</t>
+          <t>['+91-99887-76655']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Rajesh Kumar' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '9988776655'; standard E.164 is '+91-99887-76655'</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2914,32 +2840,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iss_dup_b64513</t>
+          <t>iss_fmt_012588</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rajesh Kumar</t>
+          <t>9988776655</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['Rajesh Kumar']</t>
+          <t>['+91-99887-76655']</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Rajesh Kumar' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '9988776655'; standard E.164 is '+91-99887-76655'</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2956,32 +2882,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iss_dup_bbc1e0</t>
+          <t>iss_fmt_fe17af</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rajesh Kumar</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['Rajesh Kumar']</t>
+          <t>['+91-98765-43210']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Rajesh Kumar' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '9876543210'; standard E.164 is '+91-98765-43210'</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2998,32 +2924,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iss_dup_939301</t>
+          <t>iss_fmt_ad219a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>+91 9123456780</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['Priya Sharma']</t>
+          <t>['+91-91234-56780']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Priya Sharma' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '+91 9123456780'; standard E.164 is '+91-91234-56780'</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3040,32 +2966,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iss_dup_880fff</t>
+          <t>iss_fmt_62e214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amit Patel</t>
+          <t>555-234-5678</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['Amit Patel']</t>
+          <t>['+1-555-234-5678']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Amit Patel' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '555-234-5678'; standard E.164 is '+1-555-234-5678'</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3082,32 +3008,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iss_dup_be1f45</t>
+          <t>iss_fmt_9eeeeb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CustomerName</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sarah Jenkins</t>
+          <t>9440123456</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['Sarah Jenkins']</t>
+          <t>['+91-94401-23456']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Exact duplicate CustomerName detected: 'Sarah Jenkins' (Page 1 and Page 1)</t>
+          <t>Inconsistent phone format '9440123456'; standard E.164 is '+91-94401-23456'</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3124,32 +3050,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iss_dup_674258</t>
+          <t>iss_datefmt_62d76b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>15/03/2023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['9876543210']</t>
+          <t>['2023-03-15']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Exact duplicate Phone detected: '9876543210' (Page 1 and Page 1)</t>
+          <t>Inconsistent date format '15/03/2023'; ISO 8601 standard is '2023-03-15'</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3166,32 +3092,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iss_dup_2c2da0</t>
+          <t>iss_datefmt_0f7e91</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+91 9123456780</t>
+          <t>04-20-2022</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['+91 9123456780']</t>
+          <t>['2022-04-20']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Exact duplicate Phone detected: '+91 9123456780' (Page 1 and Page 1)</t>
+          <t>Inconsistent date format '04-20-2022'; ISO 8601 standard is '2022-04-20'</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3208,32 +3134,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iss_dup_33dfed</t>
+          <t>iss_datefmt_31e3bf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9988776655</t>
+          <t>12/01/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['9988776655']</t>
+          <t>['2024-01-12']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Exact duplicate Phone detected: '9988776655' (Page 1 and Page 1)</t>
+          <t>Inconsistent date format '12/01/2024'; ISO 8601 standard is '2024-01-12'</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3250,37 +3176,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iss_ndup_3d8e7f</t>
+          <t>iss_datefmt_508852</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>duplicate</t>
+          <t>format_inconsistent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+1-555-234-5678</t>
+          <t>15/03/2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['555-234-5678']</t>
+          <t>['2024-03-15']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Near-duplicate Phone (88.9% similarity): '+1-555-234-5678' vs '555-234-5678'</t>
+          <t>Inconsistent date format '15/03/2024'; ISO 8601 standard is '2024-03-15'</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3292,7 +3218,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iss_fmt_47b10d</t>
+          <t>iss_datefmt_a94ae6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3302,22 +3228,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>20/04/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['+91-98765-43210']</t>
+          <t>['2024-04-20']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '9876543210'; standard E.164 is '+91-98765-43210'</t>
+          <t>Inconsistent date format '20/04/2024'; ISO 8601 standard is '2024-04-20'</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3334,7 +3260,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>iss_fmt_201f07</t>
+          <t>iss_datefmt_5ce18d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3344,22 +3270,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+91 9123456780</t>
+          <t>05-11-2023</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['+91-91234-56780']</t>
+          <t>['2023-11-05']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '+91 9123456780'; standard E.164 is '+91-91234-56780'</t>
+          <t>Inconsistent date format '05-11-2023'; ISO 8601 standard is '2023-11-05'</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3376,12 +3302,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>iss_fmt_79c12c</t>
+          <t>iss_confl_c31ba0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>format_inconsistent</t>
+          <t>conflict</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3391,22 +3317,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9988776655</t>
+          <t>+1-555-234-5678</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['+91-99887-76655']</t>
+          <t>['+91-98765-43210']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '9988776655'; standard E.164 is '+91-99887-76655'</t>
+          <t>Conflicting Phone values for 'Sarah Jenkins': +1-555-234-5678, +91-98765-43210</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3418,37 +3344,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iss_fmt_69c7b4</t>
+          <t>iss_confl_7e7bb5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>format_inconsistent</t>
+          <t>conflict</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9988776655</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['+91-99887-76655']</t>
+          <t>['Hyderabad']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '9988776655'; standard E.164 is '+91-99887-76655'</t>
+          <t>Conflicting City values for 'Sarah Jenkins': San Francisco, Hyderabad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3460,12 +3386,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iss_fmt_92e8aa</t>
+          <t>iss_confl_cc6639</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>format_inconsistent</t>
+          <t>conflict</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3475,22 +3401,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>+91-94401-23456</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['+91-98765-43210']</t>
+          <t>['+91-91234-56780']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '9876543210'; standard E.164 is '+91-98765-43210'</t>
+          <t>Conflicting Phone values for 'Suresh Reddy': +91-94401-23456, +91-91234-56780</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3502,32 +3428,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iss_fmt_83788f</t>
+          <t>iss_sem_42432b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>format_inconsistent</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>+91 9123456780</t>
+          <t>HYD</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['+91-91234-56780']</t>
+          <t>['Hyderabad']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '+91 9123456780'; standard E.164 is '+91-91234-56780'</t>
+          <t>Semantic variant 'HYD' detected for canonical city 'Hyderabad'</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3544,32 +3470,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iss_fmt_ff1ae6</t>
+          <t>iss_sem_d1e5fa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>format_inconsistent</t>
+          <t>semantic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>555-234-5678</t>
+          <t>Hyd</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['+1-555-234-5678']</t>
+          <t>['Hyderabad']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inconsistent phone format '555-234-5678'; standard E.164 is '+1-555-234-5678'</t>
+          <t>Semantic variant 'Hyd' detected for canonical city 'Hyderabad'</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3578,384 +3504,6 @@
         </is>
       </c>
       <c r="H26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>iss_fmt_b8512b</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>9440123456</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>['+91-94401-23456']</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Inconsistent phone format '9440123456'; standard E.164 is '+91-94401-23456'</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>iss_datefmt_079cd9</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>15/03/2023</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>['2023-03-15']</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '15/03/2023'; ISO 8601 standard is '2023-03-15'</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>iss_datefmt_5550d8</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>04-20-2022</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>['2022-04-20']</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '04-20-2022'; ISO 8601 standard is '2022-04-20'</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>iss_datefmt_e2aca0</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>12/01/2024</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>['2024-01-12']</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '12/01/2024'; ISO 8601 standard is '2024-01-12'</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>iss_datefmt_29fa28</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>15/03/2024</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>['2024-03-15']</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '15/03/2024'; ISO 8601 standard is '2024-03-15'</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>iss_datefmt_f04c8e</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>20/04/2024</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>['2024-04-20']</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '20/04/2024'; ISO 8601 standard is '2024-04-20'</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>iss_datefmt_7dff5c</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>format_inconsistent</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>05-11-2023</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>['2023-11-05']</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Inconsistent date format '05-11-2023'; ISO 8601 standard is '2023-11-05'</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>iss_sem_4fb77f</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>semantic</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>HYD</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>['Hyderabad']</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Semantic variant 'HYD' detected for canonical city 'Hyderabad'</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>iss_sem_a74585</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>semantic</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hyd</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>['Hyderabad']</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Semantic variant 'Hyd' detected for canonical city 'Hyderabad'</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -4015,7 +3563,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-30T15:38:29.191701+00:00</t>
+          <t>2026-09-30T19:09:19.018018+00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4025,7 +3573,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Team-NARVL\doc_extension\data\delta_document\fe975e75-1b7f-4b00-bbad-5b2f26cf3926\snapshot_v0.json</t>
+          <t>C:\Users\Anirudh Potukuchi\Desktop\Team-NARVL\doc_extension\data\delta_document\c94c4872-e531-45cc-99dc-90d908147e53\snapshot_v0.json</t>
         </is>
       </c>
     </row>
@@ -4042,7 +3590,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-30T15:38:29.202438+00:00</t>
+          <t>2026-09-30T19:09:19.025339+00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4052,7 +3600,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Team-NARVL\doc_extension\data\delta_document\fe975e75-1b7f-4b00-bbad-5b2f26cf3926\snapshot_v1.json</t>
+          <t>C:\Users\Anirudh Potukuchi\Desktop\Team-NARVL\doc_extension\data\delta_document\c94c4872-e531-45cc-99dc-90d908147e53\snapshot_v1.json</t>
         </is>
       </c>
     </row>
@@ -4069,7 +3617,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-30T15:38:29.212325+00:00</t>
+          <t>2026-09-30T19:09:19.031374+00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4079,7 +3627,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Team-NARVL\doc_extension\data\delta_document\fe975e75-1b7f-4b00-bbad-5b2f26cf3926\snapshot_v2.json</t>
+          <t>C:\Users\Anirudh Potukuchi\Desktop\Team-NARVL\doc_extension\data\delta_document\c94c4872-e531-45cc-99dc-90d908147e53\snapshot_v2.json</t>
         </is>
       </c>
     </row>
@@ -4096,7 +3644,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-30T15:38:29.220412+00:00</t>
+          <t>2026-09-30T19:09:19.036243+00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4106,7 +3654,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Team-NARVL\doc_extension\data\delta_document\fe975e75-1b7f-4b00-bbad-5b2f26cf3926\snapshot_v3.json</t>
+          <t>C:\Users\Anirudh Potukuchi\Desktop\Team-NARVL\doc_extension\data\delta_document\c94c4872-e531-45cc-99dc-90d908147e53\snapshot_v3.json</t>
         </is>
       </c>
     </row>
